--- a/resources/outputs_schema_data_analytics_mortality_roster_template.xlsx
+++ b/resources/outputs_schema_data_analytics_mortality_roster_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A14877C-0AB9-46EE-887D-336B2784132B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABB93B5-166E-478E-85B8-7106D1432643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22785" yWindow="2820" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="59">
   <si>
     <t>output_name</t>
   </si>
@@ -175,10 +175,28 @@
     <t>sex,age_years,age_months_cat,stratum</t>
   </si>
   <si>
-    <t>variable=c(@variable_map$sex, @variable_map$age_years, @variable_map$age_months_cat),stat_type=c("percentage","mean","percentage"),variable_label=c(@variable_label$sex, @variable_label$age_years,@variable_label$age_months_cat)</t>
-  </si>
-  <si>
-    <t>variable=c(@variable_map$sex, @variable_map$age_years, @variable_map$age_months_cat),stat_type=c("percentage","mean","percentage"),variable_label=c(@variable_label$sex, @variable_label$age_years,@variable_label$age_months_cat),disaggregation_wide=TRUE,disaggregation=@variable_map$stratum</t>
+    <t>variable=c(@variable_map$sex, @variable_map$age_years, @variable_map$age_months_cat),stat_type=c("percentage","mean","percentage"),variable_label=c(@variable_label$sex, @variable_label$age_years,@variable_label$age_months_cat), show_ci=TRUE,disaggregation_wide=TRUE,disaggregation=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>variable=c(@variable_map$sex, @variable_map$age_years, @variable_map$age_months_cat),stat_type=c("percentage","mean","percentage"), show_ci=TRUE,variable_label=c(@variable_label$sex, @variable_label$age_years,@variable_label$age_months_cat)</t>
+  </si>
+  <si>
+    <t>basic_demo_table_weighted</t>
+  </si>
+  <si>
+    <t>basic_demo_table_strata_weighted</t>
+  </si>
+  <si>
+    <t>variable=c(@variable_map$sex, @variable_map$age_years, @variable_map$age_months_cat),stat_type=c("percentage","mean","percentage"), show_ci=TRUE,variable_label=c(@variable_label$sex, @variable_label$age_years,@variable_label$age_months_cat),weighted_result=TRUE,weights_col=@variable_map$weight</t>
+  </si>
+  <si>
+    <t>variable=c(@variable_map$sex, @variable_map$age_years, @variable_map$age_months_cat),stat_type=c("percentage","mean","percentage"),variable_label=c(@variable_label$sex, @variable_label$age_years,@variable_label$age_months_cat), show_ci=TRUE,disaggregation_wide=TRUE,disaggregation=@variable_map$stratum,weighted_result=TRUE,weights_col=@variable_map$weight</t>
+  </si>
+  <si>
+    <t>table_frequency_v2</t>
+  </si>
+  <si>
+    <t>survey_design</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.140625" customWidth="1"/>
@@ -1267,10 +1285,10 @@
         <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
         <v>40</v>
@@ -1279,7 +1297,7 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1296,7 +1314,7 @@
         <v>38</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
         <v>40</v>
@@ -1310,19 +1328,19 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
         <v>40</v>
@@ -1336,19 +1354,19 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H11" t="s">
         <v>40</v>
@@ -1357,6 +1375,58 @@
         <v>16</v>
       </c>
       <c r="K11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1366,10 +1436,12 @@
     <hyperlink ref="G3" r:id="rId2" display="sex_col=@variable_map$sex,age_years_col=@variable_map$age_years,sex_male_val=@value_map$sex$male,sex_female_val=@value_map$sex$female,sex_male_lab=@value_label$sex$male,sex_female_lab=@value_label$sex$female,weighted_result=TRUE,weights_col=@variable_map$weight" xr:uid="{0261052B-065C-4206-9184-DA88176D1506}"/>
     <hyperlink ref="G6" r:id="rId3" xr:uid="{7FA155E1-10AF-49C8-A797-D691ADDE6798}"/>
     <hyperlink ref="G7" r:id="rId4" xr:uid="{DB4F8BAB-6125-4797-8D13-0402504B8B10}"/>
-    <hyperlink ref="G10" r:id="rId5" xr:uid="{8C091659-4D31-4D20-B794-7578A5006901}"/>
-    <hyperlink ref="G11" r:id="rId6" xr:uid="{613E19A2-DE48-4744-8786-6E0A8F2402FC}"/>
+    <hyperlink ref="G12" r:id="rId5" xr:uid="{8C091659-4D31-4D20-B794-7578A5006901}"/>
+    <hyperlink ref="G13" r:id="rId6" xr:uid="{613E19A2-DE48-4744-8786-6E0A8F2402FC}"/>
     <hyperlink ref="G8" r:id="rId7" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{3328ECAF-4C40-4261-91D0-D039E6E20D32}"/>
     <hyperlink ref="G9" r:id="rId8" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{FC899D53-7DCC-413B-89D6-F69E9A6A500A}"/>
+    <hyperlink ref="G10" r:id="rId9" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{A4B70DE2-B443-4403-8B05-861B4430E146}"/>
+    <hyperlink ref="G11" r:id="rId10" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{7DD80563-F03F-44C8-955D-0014E913EE5C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
